--- a/DATA MASTER/MASTER_DATA.xlsx
+++ b/DATA MASTER/MASTER_DATA.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="12">
   <si>
     <t>Seller</t>
   </si>
@@ -35,6 +35,18 @@
   </si>
   <si>
     <t>5RB/12JAM</t>
+  </si>
+  <si>
+    <t>Warung</t>
+  </si>
+  <si>
+    <t>Eceu</t>
+  </si>
+  <si>
+    <t>HOME</t>
+  </si>
+  <si>
+    <t>ILHAM</t>
   </si>
 </sst>
 </file>
@@ -92,7 +104,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -107,6 +119,9 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -470,10 +485,18 @@
       <c r="Z4" s="3"/>
     </row>
     <row r="5">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
+      <c r="A5" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="4">
+        <v>500.0</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.0</v>
+      </c>
       <c r="E5" s="2"/>
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
@@ -498,10 +521,18 @@
       <c r="Z5" s="3"/>
     </row>
     <row r="6">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
+      <c r="A6" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="4">
+        <v>500.0</v>
+      </c>
+      <c r="D6" s="4">
+        <v>500.0</v>
+      </c>
       <c r="E6" s="2"/>
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
@@ -526,10 +557,18 @@
       <c r="Z6" s="3"/>
     </row>
     <row r="7">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
+      <c r="A7" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="4">
+        <v>1000.0</v>
+      </c>
+      <c r="D7" s="4">
+        <v>1000.0</v>
+      </c>
       <c r="E7" s="2"/>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
@@ -554,10 +593,18 @@
       <c r="Z7" s="3"/>
     </row>
     <row r="8">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
+      <c r="A8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="4">
+        <v>500.0</v>
+      </c>
+      <c r="D8" s="4">
+        <v>0.0</v>
+      </c>
       <c r="E8" s="2"/>
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
@@ -582,10 +629,18 @@
       <c r="Z8" s="3"/>
     </row>
     <row r="9">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
+      <c r="A9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="4">
+        <v>500.0</v>
+      </c>
+      <c r="D9" s="4">
+        <v>500.0</v>
+      </c>
       <c r="E9" s="2"/>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
@@ -610,10 +665,18 @@
       <c r="Z9" s="3"/>
     </row>
     <row r="10">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
+      <c r="A10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="5">
+        <v>500.0</v>
+      </c>
+      <c r="D10" s="5">
+        <v>500.0</v>
+      </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
@@ -638,10 +701,18 @@
       <c r="Z10" s="3"/>
     </row>
     <row r="11">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
+      <c r="A11" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="4">
+        <v>500.0</v>
+      </c>
+      <c r="D11" s="4">
+        <v>0.0</v>
+      </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
@@ -666,10 +737,18 @@
       <c r="Z11" s="3"/>
     </row>
     <row r="12">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
+      <c r="A12" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="5">
+        <v>1000.0</v>
+      </c>
+      <c r="D12" s="5">
+        <v>0.0</v>
+      </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
@@ -694,10 +773,18 @@
       <c r="Z12" s="3"/>
     </row>
     <row r="13">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
+      <c r="A13" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="5">
+        <v>2000.0</v>
+      </c>
+      <c r="D13" s="5">
+        <v>0.0</v>
+      </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
@@ -722,10 +809,18 @@
       <c r="Z13" s="3"/>
     </row>
     <row r="14">
-      <c r="A14" s="3"/>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
+      <c r="A14" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" s="4">
+        <v>500.0</v>
+      </c>
+      <c r="D14" s="4">
+        <v>0.0</v>
+      </c>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
@@ -750,10 +845,18 @@
       <c r="Z14" s="3"/>
     </row>
     <row r="15">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
+      <c r="A15" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" s="5">
+        <v>1000.0</v>
+      </c>
+      <c r="D15" s="5">
+        <v>0.0</v>
+      </c>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
@@ -778,10 +881,18 @@
       <c r="Z15" s="3"/>
     </row>
     <row r="16">
-      <c r="A16" s="3"/>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
+      <c r="A16" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="5">
+        <v>2000.0</v>
+      </c>
+      <c r="D16" s="5">
+        <v>0.0</v>
+      </c>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
